--- a/output/upload/S00027_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
+++ b/output/upload/S00027_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
@@ -2611,11 +2611,31 @@
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
-      <c r="B7" s="5" t="inlineStr"/>
-      <c r="C7" s="5" t="n"/>
-      <c r="D7" s="5" t="inlineStr"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2694,11 +2714,31 @@
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
-      <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="5" t="n"/>
-      <c r="D8" s="5" t="inlineStr"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2777,11 +2817,31 @@
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
-      <c r="B9" s="5" t="inlineStr"/>
-      <c r="C9" s="5" t="n"/>
-      <c r="D9" s="5" t="inlineStr"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2860,11 +2920,31 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
-      <c r="B10" s="5" t="inlineStr"/>
-      <c r="C10" s="5" t="n"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -2943,11 +3023,31 @@
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
-      <c r="B11" s="5" t="inlineStr"/>
-      <c r="C11" s="5" t="n"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3026,11 +3126,31 @@
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
-      <c r="B12" s="5" t="inlineStr"/>
-      <c r="C12" s="5" t="n"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3109,11 +3229,31 @@
     </row>
     <row r="13">
       <c r="A13" s="5" t="n"/>
-      <c r="B13" s="5" t="inlineStr"/>
-      <c r="C13" s="5" t="n"/>
-      <c r="D13" s="5" t="inlineStr"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3192,11 +3332,31 @@
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
-      <c r="B14" s="5" t="inlineStr"/>
-      <c r="C14" s="5" t="n"/>
-      <c r="D14" s="5" t="inlineStr"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3274,8 +3434,31 @@
       <c r="AW14" s="6" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3319,8 +3502,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3364,8 +3570,31 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3409,8 +3638,31 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G18" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3454,8 +3706,31 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G19" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3499,8 +3774,31 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3544,8 +3842,31 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3589,8 +3910,31 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G22" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3634,8 +3978,31 @@
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G23" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3679,8 +4046,31 @@
       </c>
     </row>
     <row r="24">
-      <c r="B24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G24" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3724,8 +4114,31 @@
       </c>
     </row>
     <row r="25">
-      <c r="B25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3769,8 +4182,31 @@
       </c>
     </row>
     <row r="26">
-      <c r="B26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3814,8 +4250,31 @@
       </c>
     </row>
     <row r="27">
-      <c r="B27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3859,8 +4318,31 @@
       </c>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3904,8 +4386,31 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3949,8 +4454,31 @@
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -3994,8 +4522,31 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4039,8 +4590,31 @@
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4084,8 +4658,31 @@
       </c>
     </row>
     <row r="33">
-      <c r="B33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4129,8 +4726,31 @@
       </c>
     </row>
     <row r="34">
-      <c r="B34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4174,8 +4794,31 @@
       </c>
     </row>
     <row r="35">
-      <c r="B35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4219,8 +4862,31 @@
       </c>
     </row>
     <row r="36">
-      <c r="B36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4264,8 +4930,31 @@
       </c>
     </row>
     <row r="37">
-      <c r="B37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4309,8 +4998,31 @@
       </c>
     </row>
     <row r="38">
-      <c r="B38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4354,8 +5066,31 @@
       </c>
     </row>
     <row r="39">
-      <c r="B39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4399,8 +5134,31 @@
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4444,8 +5202,31 @@
       </c>
     </row>
     <row r="41">
-      <c r="B41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4489,8 +5270,31 @@
       </c>
     </row>
     <row r="42">
-      <c r="B42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4534,8 +5338,31 @@
       </c>
     </row>
     <row r="43">
-      <c r="B43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4579,8 +5406,31 @@
       </c>
     </row>
     <row r="44">
-      <c r="B44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4624,8 +5474,31 @@
       </c>
     </row>
     <row r="45">
-      <c r="B45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4669,8 +5542,31 @@
       </c>
     </row>
     <row r="46">
-      <c r="B46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4714,8 +5610,31 @@
       </c>
     </row>
     <row r="47">
-      <c r="B47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4759,8 +5678,31 @@
       </c>
     </row>
     <row r="48">
-      <c r="B48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G48" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4804,8 +5746,31 @@
       </c>
     </row>
     <row r="49">
-      <c r="B49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4849,8 +5814,31 @@
       </c>
     </row>
     <row r="50">
-      <c r="B50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G50" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4894,8 +5882,31 @@
       </c>
     </row>
     <row r="51">
-      <c r="B51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4939,8 +5950,31 @@
       </c>
     </row>
     <row r="52">
-      <c r="B52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G52" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -4984,8 +6018,31 @@
       </c>
     </row>
     <row r="53">
-      <c r="B53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5029,8 +6086,31 @@
       </c>
     </row>
     <row r="54">
-      <c r="B54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G54" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5074,8 +6154,31 @@
       </c>
     </row>
     <row r="55">
-      <c r="B55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5119,8 +6222,31 @@
       </c>
     </row>
     <row r="56">
-      <c r="B56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G56" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5164,8 +6290,31 @@
       </c>
     </row>
     <row r="57">
-      <c r="B57" t="inlineStr"/>
-      <c r="D57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G57" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5209,8 +6358,31 @@
       </c>
     </row>
     <row r="58">
-      <c r="B58" t="inlineStr"/>
-      <c r="D58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5254,8 +6426,31 @@
       </c>
     </row>
     <row r="59">
-      <c r="B59" t="inlineStr"/>
-      <c r="D59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G59" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5299,8 +6494,31 @@
       </c>
     </row>
     <row r="60">
-      <c r="B60" t="inlineStr"/>
-      <c r="D60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G60" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5344,8 +6562,31 @@
       </c>
     </row>
     <row r="61">
-      <c r="B61" t="inlineStr"/>
-      <c r="D61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G61" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5389,8 +6630,31 @@
       </c>
     </row>
     <row r="62">
-      <c r="B62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G62" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5434,8 +6698,31 @@
       </c>
     </row>
     <row r="63">
-      <c r="B63" t="inlineStr"/>
-      <c r="D63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G63" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5479,8 +6766,31 @@
       </c>
     </row>
     <row r="64">
-      <c r="B64" t="inlineStr"/>
-      <c r="D64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G64" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5524,8 +6834,31 @@
       </c>
     </row>
     <row r="65">
-      <c r="B65" t="inlineStr"/>
-      <c r="D65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G65" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5569,8 +6902,31 @@
       </c>
     </row>
     <row r="66">
-      <c r="B66" t="inlineStr"/>
-      <c r="D66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G66" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5614,8 +6970,31 @@
       </c>
     </row>
     <row r="67">
-      <c r="B67" t="inlineStr"/>
-      <c r="D67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G67" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5659,8 +7038,31 @@
       </c>
     </row>
     <row r="68">
-      <c r="B68" t="inlineStr"/>
-      <c r="D68" t="inlineStr"/>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G68" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5704,8 +7106,31 @@
       </c>
     </row>
     <row r="69">
-      <c r="B69" t="inlineStr"/>
-      <c r="D69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G69" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5749,8 +7174,31 @@
       </c>
     </row>
     <row r="70">
-      <c r="B70" t="inlineStr"/>
-      <c r="D70" t="inlineStr"/>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G70" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5794,8 +7242,31 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr"/>
-      <c r="D71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G71" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5839,8 +7310,31 @@
       </c>
     </row>
     <row r="72">
-      <c r="B72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G72" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5884,8 +7378,31 @@
       </c>
     </row>
     <row r="73">
-      <c r="B73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G73" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5929,8 +7446,31 @@
       </c>
     </row>
     <row r="74">
-      <c r="B74" t="inlineStr"/>
-      <c r="D74" t="inlineStr"/>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G74" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -5974,8 +7514,31 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr"/>
-      <c r="D75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G75" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6019,8 +7582,31 @@
       </c>
     </row>
     <row r="76">
-      <c r="B76" t="inlineStr"/>
-      <c r="D76" t="inlineStr"/>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G76" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6064,8 +7650,31 @@
       </c>
     </row>
     <row r="77">
-      <c r="B77" t="inlineStr"/>
-      <c r="D77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G77" t="inlineStr">
         <is>
           <t>20260201</t>
@@ -6109,8 +7718,31 @@
       </c>
     </row>
     <row r="78">
-      <c r="B78" t="inlineStr"/>
-      <c r="D78" t="inlineStr"/>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>2258A01</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>22581</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
       <c r="G78" t="inlineStr">
         <is>
           <t>20260201</t>

--- a/output/upload/S00027_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
+++ b/output/upload/S00027_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
@@ -2623,7 +2623,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -2829,7 +2829,7 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -3138,7 +3138,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3650,7 +3650,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -3718,7 +3718,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3854,7 +3854,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3922,7 +3922,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4330,7 +4330,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4398,7 +4398,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -5010,7 +5010,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -5078,7 +5078,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -5350,7 +5350,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -5418,7 +5418,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -5554,7 +5554,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -5690,7 +5690,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6030,7 +6030,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -6098,7 +6098,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -6302,7 +6302,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -6574,7 +6574,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -6642,7 +6642,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6846,7 +6846,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6914,7 +6914,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7050,7 +7050,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7186,7 +7186,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7322,7 +7322,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7390,7 +7390,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7662,7 +7662,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22581</t>
+          <t>2258001</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">

--- a/output/upload/S00027_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
+++ b/output/upload/S00027_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW78"/>
+  <dimension ref="A1:AW110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17.484375" customWidth="1" min="1" max="1"/>
@@ -3436,22 +3436,22 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258002</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3504,22 +3504,22 @@
     <row r="16">
       <c r="B16" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258002</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3572,22 +3572,22 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A02</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258002</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3640,22 +3640,22 @@
     <row r="18">
       <c r="B18" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A02</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258002</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3708,22 +3708,22 @@
     <row r="19">
       <c r="B19" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A02</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258002</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3776,22 +3776,22 @@
     <row r="20">
       <c r="B20" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A02</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258002</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3844,22 +3844,22 @@
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A02</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258002</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3912,22 +3912,22 @@
     <row r="22">
       <c r="B22" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A02</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258002</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(1년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3980,22 +3980,22 @@
     <row r="23">
       <c r="B23" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258003</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4048,22 +4048,22 @@
     <row r="24">
       <c r="B24" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258003</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4116,22 +4116,22 @@
     <row r="25">
       <c r="B25" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258003</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4184,22 +4184,22 @@
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258003</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -4252,22 +4252,22 @@
     <row r="27">
       <c r="B27" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258003</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4320,22 +4320,22 @@
     <row r="28">
       <c r="B28" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258003</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4388,22 +4388,22 @@
     <row r="29">
       <c r="B29" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258003</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4456,22 +4456,22 @@
     <row r="30">
       <c r="B30" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258003</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(2년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4524,22 +4524,22 @@
     <row r="31">
       <c r="B31" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258004</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4592,22 +4592,22 @@
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A04</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258004</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4660,22 +4660,22 @@
     <row r="33">
       <c r="B33" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A04</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258004</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4728,22 +4728,22 @@
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A04</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258004</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -4796,22 +4796,22 @@
     <row r="35">
       <c r="B35" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A04</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258004</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4864,22 +4864,22 @@
     <row r="36">
       <c r="B36" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A04</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258004</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -4932,22 +4932,22 @@
     <row r="37">
       <c r="B37" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A04</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258004</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -5000,22 +5000,22 @@
     <row r="38">
       <c r="B38" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A04</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258004</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(3년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -5068,22 +5068,22 @@
     <row r="39">
       <c r="B39" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258005</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -5136,22 +5136,22 @@
     <row r="40">
       <c r="B40" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258005</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -5204,22 +5204,22 @@
     <row r="41">
       <c r="B41" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258005</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -5272,22 +5272,22 @@
     <row r="42">
       <c r="B42" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258005</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -5340,22 +5340,22 @@
     <row r="43">
       <c r="B43" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258005</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -5408,22 +5408,22 @@
     <row r="44">
       <c r="B44" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258005</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5476,22 +5476,22 @@
     <row r="45">
       <c r="B45" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258005</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5544,22 +5544,22 @@
     <row r="46">
       <c r="B46" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258005</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(4년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -5612,22 +5612,22 @@
     <row r="47">
       <c r="B47" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258006</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5680,22 +5680,22 @@
     <row r="48">
       <c r="B48" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258006</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5748,22 +5748,22 @@
     <row r="49">
       <c r="B49" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258006</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5816,22 +5816,22 @@
     <row r="50">
       <c r="B50" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258006</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5884,22 +5884,22 @@
     <row r="51">
       <c r="B51" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258006</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5952,22 +5952,22 @@
     <row r="52">
       <c r="B52" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258006</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -6020,22 +6020,22 @@
     <row r="53">
       <c r="B53" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258006</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6088,22 +6088,22 @@
     <row r="54">
       <c r="B54" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A06</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258006</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(5년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -6156,22 +6156,22 @@
     <row r="55">
       <c r="B55" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A07</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258007</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6224,22 +6224,22 @@
     <row r="56">
       <c r="B56" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A07</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258007</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -6292,22 +6292,22 @@
     <row r="57">
       <c r="B57" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A07</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258007</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6360,22 +6360,22 @@
     <row r="58">
       <c r="B58" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A07</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258007</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -6428,22 +6428,22 @@
     <row r="59">
       <c r="B59" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A07</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258007</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -6496,22 +6496,22 @@
     <row r="60">
       <c r="B60" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A07</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258007</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6564,22 +6564,22 @@
     <row r="61">
       <c r="B61" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A07</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258007</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -6632,22 +6632,22 @@
     <row r="62">
       <c r="B62" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A07</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258007</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -6700,22 +6700,22 @@
     <row r="63">
       <c r="B63" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A08</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258008</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -6768,22 +6768,22 @@
     <row r="64">
       <c r="B64" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A08</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258008</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6836,22 +6836,22 @@
     <row r="65">
       <c r="B65" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A08</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258008</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -6904,22 +6904,22 @@
     <row r="66">
       <c r="B66" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A08</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258008</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6972,22 +6972,22 @@
     <row r="67">
       <c r="B67" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A08</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258008</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7040,22 +7040,22 @@
     <row r="68">
       <c r="B68" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A08</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258008</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7108,22 +7108,22 @@
     <row r="69">
       <c r="B69" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A08</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258008</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7176,22 +7176,22 @@
     <row r="70">
       <c r="B70" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A08</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258008</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 일반가입형 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7244,22 +7244,22 @@
     <row r="71">
       <c r="B71" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A09</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258009</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7312,22 +7312,22 @@
     <row r="72">
       <c r="B72" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A09</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258009</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7380,22 +7380,22 @@
     <row r="73">
       <c r="B73" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A09</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258009</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7448,22 +7448,22 @@
     <row r="74">
       <c r="B74" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A09</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258009</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7516,22 +7516,22 @@
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A09</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258009</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7584,22 +7584,22 @@
     <row r="76">
       <c r="B76" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A09</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258009</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7652,22 +7652,22 @@
     <row r="77">
       <c r="B77" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A09</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258009</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7720,22 +7720,22 @@
     <row r="78">
       <c r="B78" t="inlineStr">
         <is>
-          <t>2258A01</t>
+          <t>2258A09</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2258001</t>
+          <t>2258009</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 간편가입형(0년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(6년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7780,6 +7780,2182 @@
         <v>30</v>
       </c>
       <c r="O78" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>2258A10</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2258010</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L79" t="n">
+        <v>90</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N79" t="n">
+        <v>10</v>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>2258A10</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2258010</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L80" t="n">
+        <v>90</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>15</v>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2258A10</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>2258010</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L81" t="n">
+        <v>90</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N81" t="n">
+        <v>20</v>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2258A10</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>2258010</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L82" t="n">
+        <v>90</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>30</v>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2258A10</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>2258010</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L83" t="n">
+        <v>999</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>10</v>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2258A10</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>2258010</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L84" t="n">
+        <v>999</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>15</v>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2258A10</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2258010</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L85" t="n">
+        <v>999</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>20</v>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2258A10</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>2258010</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(7년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L86" t="n">
+        <v>999</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>30</v>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>2258A11</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>2258011</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L87" t="n">
+        <v>90</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>10</v>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2258A11</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>2258011</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L88" t="n">
+        <v>90</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>15</v>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>2258A11</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2258011</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L89" t="n">
+        <v>90</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>20</v>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>2258A11</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2258011</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L90" t="n">
+        <v>90</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>30</v>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>2258A11</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>2258011</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L91" t="n">
+        <v>999</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>10</v>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2258A11</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2258011</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>999</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>15</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>2258A11</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2258011</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>999</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>20</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>2258A11</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2258011</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(8년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>999</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>30</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2258A12</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>2258012</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>90</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>10</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>2258A12</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>2258012</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>90</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>15</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>2258A12</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>2258012</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>90</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>20</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2258A12</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2258012</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>90</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>30</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>2258A12</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2258012</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>999</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>10</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2258A12</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>2258012</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>999</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>15</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2258A12</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>2258012</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>999</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>20</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2258A12</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>2258012</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(9년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>999</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>30</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2258A13</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2258013</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>90</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>10</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2258A13</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2258013</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>90</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>15</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2258A13</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2258013</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>90</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>20</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2258A13</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2258013</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>X90</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>90</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>30</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2258A13</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2258013</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>N10</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>999</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>10</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2258A13</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2258013</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>N15</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>999</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>15</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2258A13</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2258013</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>N20</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>999</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>20</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>1,2,3,4,7</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2258A13</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2258013</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>한화생명 시그니처 H통합건강보험 무배당(납입면제형) 건강가입형(10년) 해약환급금 미지급형(납입기간중 0%, 납입기간후 50%)</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>S00027</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>20260201</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>99991231</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>A999</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>N30</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>999</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>30</v>
+      </c>
+      <c r="O110" t="inlineStr">
         <is>
           <t>1,2,3,4,7</t>
         </is>

--- a/output/upload/S00027_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
+++ b/output/upload/S00027_2258_시그니처_H통합건강보험_무배당_납입면제형.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="세트속성값" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
